--- a/excel-files/NAVOTAS/DAGAT-DAGATAN ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/NAVOTAS/DAGAT-DAGATAN ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32A6FC48-3080-427C-AFF5-B78EBBEA8574}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F76B9ABB-39F2-44D7-A7D8-E7D12869B8F3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Math</t>
   </si>
   <si>
+    <t>CO</t>
+  </si>
+  <si>
     <t>Science</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
   </si>
   <si>
     <t>Filipino</t>
-  </si>
-  <si>
-    <t>CO</t>
   </si>
   <si>
     <t>Araling Panlipunan</t>
@@ -742,6 +742,12 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -753,12 +759,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3542,7 +3542,9 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1">
+        <v>471</v>
+      </c>
       <c r="D3" s="1">
         <v>735</v>
       </c>
@@ -3558,7 +3560,7 @@
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>735</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1">
@@ -3701,17 +3703,25 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
+      <c r="C11" s="1">
+        <v>527</v>
+      </c>
+      <c r="D11" s="1">
+        <v>637</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
         <v>0</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="19.149999999999999">
@@ -3804,7 +3814,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -3874,7 +3884,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -3894,7 +3904,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1">
         <v>583</v>
@@ -3906,7 +3916,7 @@
         <v>2024</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
@@ -3934,7 +3944,7 @@
         <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
@@ -3962,7 +3972,7 @@
         <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
@@ -3980,17 +3990,25 @@
       <c r="B25" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="5"/>
+      <c r="C25" s="1">
+        <v>583</v>
+      </c>
+      <c r="D25" s="1">
+        <v>816</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="33.75" customHeight="1">
@@ -3998,19 +4016,27 @@
         <v>4</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="1">
+        <v>583</v>
+      </c>
+      <c r="D26" s="1">
+        <v>816</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="5"/>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="33.75" customHeight="1">
@@ -4020,17 +4046,25 @@
       <c r="B27" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="5"/>
+      <c r="C27" s="1">
+        <v>583</v>
+      </c>
+      <c r="D27" s="1">
+        <v>816</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2024</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="27.75" customHeight="1">
@@ -4060,17 +4094,25 @@
       <c r="B29" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>583</v>
+      </c>
+      <c r="D29" s="1">
+        <v>816</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -4088,19 +4130,27 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="C31" s="1">
+        <v>559</v>
+      </c>
+      <c r="D31" s="1">
+        <v>697</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
         <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4108,7 +4158,7 @@
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -4180,7 +4230,7 @@
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
@@ -4196,19 +4246,27 @@
         <v>5</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="1">
+        <v>559</v>
+      </c>
+      <c r="D36" s="1">
+        <v>697</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4218,17 +4276,25 @@
       <c r="B37" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="5"/>
+      <c r="C37" s="1">
+        <v>559</v>
+      </c>
+      <c r="D37" s="1">
+        <v>697</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2025</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4238,17 +4304,25 @@
       <c r="B38" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>559</v>
+      </c>
+      <c r="D38" s="1">
+        <v>697</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="27.75" customHeight="1">
@@ -4286,7 +4360,7 @@
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -4306,7 +4380,7 @@
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -4386,7 +4460,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -4476,7 +4550,7 @@
         <v>7</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="10"/>
@@ -4496,7 +4570,7 @@
         <v>7</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
@@ -4576,7 +4650,7 @@
         <v>7</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
@@ -4666,7 +4740,7 @@
         <v>8</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="10"/>
       <c r="D61" s="10"/>
@@ -4686,7 +4760,7 @@
         <v>8</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C62" s="10"/>
       <c r="D62" s="10"/>
@@ -4766,7 +4840,7 @@
         <v>8</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
@@ -4856,7 +4930,7 @@
         <v>9</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
@@ -4876,7 +4950,7 @@
         <v>9</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
@@ -4956,7 +5030,7 @@
         <v>9</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C76" s="10"/>
       <c r="D76" s="10"/>
@@ -5046,7 +5120,7 @@
         <v>10</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="10"/>
@@ -5066,7 +5140,7 @@
         <v>10</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C82" s="10"/>
       <c r="D82" s="10"/>
@@ -5146,7 +5220,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="10"/>
@@ -5398,10 +5472,10 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E2:E6 E8:E12 E14:E19 E21:E29 E81:E89 E41:E49 E51:E59 E61:E69 E71:E79 E31:E39" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F91:F98 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5414,7 +5488,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5444,38 +5518,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -5514,10 +5588,10 @@
       <c r="L2" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -5550,10 +5624,10 @@
       <c r="X2" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>60</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -5989,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="5">
@@ -6058,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="5">
@@ -6411,24 +6485,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999">
+    <row r="17" spans="1:27" ht="19.5">
       <c r="A17" s="1">
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>527</v>
+      </c>
       <c r="D17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="3"/>
@@ -6436,14 +6512,21 @@
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="5"/>
+        <v>4216</v>
+      </c>
+      <c r="K17" s="5">
+        <f>524*8</f>
+        <v>4192</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
@@ -6451,14 +6534,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="13"/>
@@ -6466,14 +6549,14 @@
       </c>
       <c r="V17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="15"/>
@@ -6549,24 +6632,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="C19" s="1">
+        <v>527</v>
+      </c>
       <c r="D19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -6574,14 +6659,21 @@
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="5"/>
+        <v>4216</v>
+      </c>
+      <c r="K19" s="5">
+        <f>524*8</f>
+        <v>4192</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="11"/>
@@ -6589,14 +6681,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="13"/>
@@ -6604,14 +6696,14 @@
       </c>
       <c r="V19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4216</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="15"/>
@@ -6623,7 +6715,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="5">
@@ -6982,7 +7074,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="5">
@@ -7189,7 +7281,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="5">
@@ -7258,7 +7350,7 @@
         <v>3</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="5">
@@ -7410,7 +7502,7 @@
         <v>4</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="5">
@@ -7479,7 +7571,7 @@
         <v>4</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="5">
@@ -7755,7 +7847,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="5">
@@ -8040,24 +8132,26 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.149999999999999">
+    <row r="43" spans="1:27" ht="19.5">
       <c r="A43" s="1">
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>16</v>
+      </c>
+      <c r="C43" s="1">
+        <v>559</v>
+      </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8065,29 +8159,36 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K43" s="5"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="5"/>
+        <v>4472</v>
+      </c>
+      <c r="K43" s="5">
+        <f>560*8</f>
+        <v>4480</v>
+      </c>
+      <c r="L43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8095,14 +8196,14 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
@@ -8114,7 +8215,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -8178,24 +8279,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>559</v>
+      </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8203,29 +8306,36 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="5"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="5"/>
+        <v>4472</v>
+      </c>
+      <c r="K45" s="5">
+        <f>560*8</f>
+        <v>4480</v>
+      </c>
+      <c r="L45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8233,14 +8343,14 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
@@ -8316,7 +8426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8390,7 +8500,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -8680,7 +8790,7 @@
         <v>6</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="5">
@@ -8749,7 +8859,7 @@
         <v>6</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="5">
@@ -9025,7 +9135,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="5">
@@ -9315,7 +9425,7 @@
         <v>7</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="12">
@@ -9384,7 +9494,7 @@
         <v>7</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C64" s="10"/>
       <c r="D64" s="12">
@@ -9660,7 +9770,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -9950,7 +10060,7 @@
         <v>8</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="10"/>
       <c r="D73" s="12">
@@ -10019,7 +10129,7 @@
         <v>8</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -10295,7 +10405,7 @@
         <v>8</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="10"/>
       <c r="D78" s="12">
@@ -10585,7 +10695,7 @@
         <v>9</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="12">
@@ -10654,7 +10764,7 @@
         <v>9</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -10930,7 +11040,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C88" s="10"/>
       <c r="D88" s="12">
@@ -11220,7 +11330,7 @@
         <v>10</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="12">
@@ -11289,7 +11399,7 @@
         <v>10</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C94" s="10"/>
       <c r="D94" s="12">
@@ -11565,7 +11675,7 @@
         <v>10</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -13402,191 +13512,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
+    <protectedRange sqref="C2:C3 C14:C16 C23:C31 C33:C41 C44 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C20:C21 C18 C46:C51" name="Textbooks"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 K14:L21 K43:L51" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="C19 C17" name="Textbooks_1"/>
+    <protectedRange sqref="C45" name="Textbooks_3"/>
+    <protectedRange sqref="C43" name="Textbooks_4"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13599,8 +13532,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 L33:L41 F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -13618,7 +13551,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13648,38 +13581,38 @@
   <sheetData>
     <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
       <c r="B1" s="35"/>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="41" t="s">
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="42" t="s">
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
-      <c r="S1" s="42"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="43" t="s">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44"/>
+      <c r="S1" s="44"/>
+      <c r="T1" s="44"/>
+      <c r="U1" s="44"/>
+      <c r="V1" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43"/>
-      <c r="AA1" s="43"/>
+      <c r="W1" s="45"/>
+      <c r="X1" s="45"/>
+      <c r="Y1" s="45"/>
+      <c r="Z1" s="45"/>
+      <c r="AA1" s="45"/>
     </row>
     <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
       <c r="A2" s="15" t="s">
@@ -13718,10 +13651,10 @@
       <c r="L2" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="44" t="s">
+      <c r="M2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="40" t="s">
         <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
@@ -13754,10 +13687,10 @@
       <c r="X2" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="Y2" s="45" t="s">
+      <c r="Y2" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="Z2" s="45" t="s">
+      <c r="Z2" s="41" t="s">
         <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
@@ -14114,7 +14047,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="5">
@@ -14183,7 +14116,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="5">
@@ -14667,7 +14600,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="5">
@@ -14736,7 +14669,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="5">
@@ -15082,7 +15015,7 @@
         <v>3</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="5">
@@ -15289,7 +15222,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="5">
@@ -15358,7 +15291,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="5">
@@ -15497,7 +15430,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="5">
@@ -15566,7 +15499,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="5">
@@ -15842,7 +15775,7 @@
         <v>4</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="5">
@@ -16257,7 +16190,7 @@
         <v>5</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="5">
@@ -16326,7 +16259,7 @@
         <v>5</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="5">
@@ -16602,7 +16535,7 @@
         <v>5</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="5">
@@ -17017,7 +16950,7 @@
         <v>6</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="5">
@@ -17086,7 +17019,7 @@
         <v>6</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="5">
@@ -17362,7 +17295,7 @@
         <v>6</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="5">
@@ -17777,7 +17710,7 @@
         <v>7</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="10"/>
       <c r="D67" s="12">
@@ -17846,7 +17779,7 @@
         <v>7</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C68" s="10"/>
       <c r="D68" s="12">
@@ -18122,7 +18055,7 @@
         <v>7</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C72" s="10"/>
       <c r="D72" s="12">
@@ -18537,7 +18470,7 @@
         <v>8</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="10"/>
       <c r="D79" s="12">
@@ -18606,7 +18539,7 @@
         <v>8</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C80" s="10"/>
       <c r="D80" s="12">
@@ -18882,7 +18815,7 @@
         <v>8</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="10"/>
       <c r="D84" s="12">
@@ -19297,7 +19230,7 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="12">
@@ -19366,7 +19299,7 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="10"/>
       <c r="D92" s="12">
@@ -19642,7 +19575,7 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C96" s="10"/>
       <c r="D96" s="12">
@@ -19982,7 +19915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="19.5">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20057,7 +19990,7 @@
         <v>10</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="12">
@@ -20126,7 +20059,7 @@
         <v>10</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C104" s="10"/>
       <c r="D104" s="12">
@@ -20402,7 +20335,7 @@
         <v>10</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C108" s="10"/>
       <c r="D108" s="12">
@@ -21875,186 +21808,6 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
@@ -22072,8 +21825,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122 X91:X101 F3:F10 F12:F19 F21:F29 F31:F41 F43:F53 F55:F65 F67:F77 F79:F89 F91:F101 F103:F113 F115:F122 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X103:X113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
